--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE7806E-26A6-4F8E-9C96-6E0D52C98C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33936E8-1D16-40BA-A635-B70D3F3E0D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>correo</t>
   </si>
@@ -28,13 +28,10 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>negocios@partnertech.pe</t>
+    <t>fguerrero@partnertech.pe</t>
   </si>
   <si>
-    <t>acardozo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Alexandra</t>
+    <t>Franco</t>
   </si>
 </sst>
 </file>
@@ -445,14 +442,12 @@
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
@@ -920,7 +915,6 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{14B04BBB-6586-4521-B6B4-EAC074EA5C3B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33936E8-1D16-40BA-A635-B70D3F3E0D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8603CA5-0171-4EEF-B4E1-4706011C6735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="6">
   <si>
     <t>correo</t>
   </si>
@@ -32,6 +32,12 @@
   </si>
   <si>
     <t>Franco</t>
+  </si>
+  <si>
+    <t>negocios@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Negocios</t>
   </si>
 </sst>
 </file>
@@ -447,23 +453,53 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -915,6 +951,12 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{1506B0AD-A666-43C9-B22C-F0D9CBDE36FC}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{42B119AC-C9BC-4C8E-85B6-21905E564B35}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{FE12341A-BE97-4A2A-A6E4-9A404D382319}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{C9B11FA1-7E98-484A-889D-469775720592}"/>
+    <hyperlink ref="A5" r:id="rId6" xr:uid="{29A2EE41-D241-4DF0-BF6D-CDEDF506E9F4}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{29147927-55D1-4B64-8574-EDFBB03E6D12}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8603CA5-0171-4EEF-B4E1-4706011C6735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D6D2D2-3AF4-43E3-9742-4881E73C3803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
   <si>
     <t>correo</t>
   </si>
@@ -34,10 +34,7 @@
     <t>Franco</t>
   </si>
   <si>
-    <t>negocios@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Negocios</t>
+    <t>guerrerofranco1429@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -454,10 +451,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -470,7 +467,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -478,7 +475,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -490,16 +487,11 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -951,12 +943,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{1506B0AD-A666-43C9-B22C-F0D9CBDE36FC}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{42B119AC-C9BC-4C8E-85B6-21905E564B35}"/>
-    <hyperlink ref="A6" r:id="rId4" xr:uid="{FE12341A-BE97-4A2A-A6E4-9A404D382319}"/>
-    <hyperlink ref="A7" r:id="rId5" xr:uid="{C9B11FA1-7E98-484A-889D-469775720592}"/>
-    <hyperlink ref="A5" r:id="rId6" xr:uid="{29A2EE41-D241-4DF0-BF6D-CDEDF506E9F4}"/>
-    <hyperlink ref="A8" r:id="rId7" xr:uid="{29147927-55D1-4B64-8574-EDFBB03E6D12}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{543B3D8C-D11A-4AF5-8B5B-37C787D83E3D}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{76B4B425-C212-4A66-A68F-050FDA124E28}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{A99D16AB-F7B8-4448-9F1C-BE8A3AD4C7B6}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{745BC159-71CF-4013-93D6-A8CA789253FC}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{75CE24CC-9930-48F3-BC80-7E8359AC0CC2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorio\Correos-Masivos-Partner-Tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D6D2D2-3AF4-43E3-9742-4881E73C3803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC68F386-D787-4BC1-9EEE-DA7DC6362D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>correo</t>
   </si>
@@ -34,14 +34,23 @@
     <t>Franco</t>
   </si>
   <si>
-    <t>guerrerofranco1429@gmail.com</t>
+    <t>ronnalramirez@gmail.com</t>
+  </si>
+  <si>
+    <t>Ronnal</t>
+  </si>
+  <si>
+    <t>acardozo@partnertech.pe</t>
+  </si>
+  <si>
+    <t>Alexandra</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,6 +84,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,7 +132,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -124,6 +140,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -451,44 +468,29 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
+      <c r="A6" s="2"/>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
+      <c r="A7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -943,11 +945,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{543B3D8C-D11A-4AF5-8B5B-37C787D83E3D}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{76B4B425-C212-4A66-A68F-050FDA124E28}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{A99D16AB-F7B8-4448-9F1C-BE8A3AD4C7B6}"/>
-    <hyperlink ref="A6" r:id="rId5" xr:uid="{745BC159-71CF-4013-93D6-A8CA789253FC}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{75CE24CC-9930-48F3-BC80-7E8359AC0CC2}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{E4BE2727-FD9D-4DAD-A064-E612963F5076}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{2710A10A-7C12-4E4F-8843-6A99EA6299DB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorio\Correos-Masivos-Partner-Tech\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC68F386-D787-4BC1-9EEE-DA7DC6362D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186DC70A-9A80-4E46-BFD3-B67D3A7EC960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="4">
   <si>
     <t>correo</t>
   </si>
@@ -28,29 +28,17 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>fguerrero@partnertech.pe</t>
-  </si>
-  <si>
     <t>Franco</t>
   </si>
   <si>
-    <t>ronnalramirez@gmail.com</t>
-  </si>
-  <si>
-    <t>Ronnal</t>
-  </si>
-  <si>
-    <t>acardozo@partnertech.pe</t>
-  </si>
-  <si>
-    <t>Alexandra</t>
+    <t>guerrerofranco1429@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,13 +72,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -132,7 +113,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -140,7 +121,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -460,61 +440,76 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4"/>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4"/>
+      <c r="A14" s="2"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
+      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
@@ -943,11 +938,6 @@
       <c r="A167" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{A7D9E44E-A359-40C4-9B11-6A027C0E0EBE}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{E4BE2727-FD9D-4DAD-A064-E612963F5076}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{2710A10A-7C12-4E4F-8843-6A99EA6299DB}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186DC70A-9A80-4E46-BFD3-B67D3A7EC960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C762E5-BB49-4CE2-BC47-D40FF0894557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/Correos.xlsx
+++ b/data/Correos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\Repositorios\correos-masivos-partner-tech\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Repositorios\Correos-Masivos-Partner-Tech\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C762E5-BB49-4CE2-BC47-D40FF0894557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF5D0FF-239D-4518-B9FF-F687968595AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="155">
   <si>
     <t>correo</t>
   </si>
@@ -28,17 +28,470 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>Franco</t>
-  </si>
-  <si>
-    <t>guerrerofranco1429@gmail.com</t>
+    <t>Miguel</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Victor</t>
+  </si>
+  <si>
+    <t>Jorge</t>
+  </si>
+  <si>
+    <t>dante.jeri@mggroup.com.pe</t>
+  </si>
+  <si>
+    <t>Dante</t>
+  </si>
+  <si>
+    <t>cxavier_63@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>jaxa13@hotmail.com</t>
+  </si>
+  <si>
+    <t>afrikakorpus@gmail.com</t>
+  </si>
+  <si>
+    <t>Jackeline</t>
+  </si>
+  <si>
+    <t>melinavelasquez09@gmail.com</t>
+  </si>
+  <si>
+    <t>Melina</t>
+  </si>
+  <si>
+    <t>mcarloscarrillo2010@gmail.com</t>
+  </si>
+  <si>
+    <t>Mirko</t>
+  </si>
+  <si>
+    <t>administracion@meacfa.com</t>
+  </si>
+  <si>
+    <t>Teodora</t>
+  </si>
+  <si>
+    <t>comercial@meacfa.com</t>
+  </si>
+  <si>
+    <t>Vanessa</t>
+  </si>
+  <si>
+    <t>amorales@moalcenter.com</t>
+  </si>
+  <si>
+    <t>Alfredo</t>
+  </si>
+  <si>
+    <t>administracion@ciclo.com.pe</t>
+  </si>
+  <si>
+    <t>Angie</t>
+  </si>
+  <si>
+    <t>alonsomqk@gmail.com</t>
+  </si>
+  <si>
+    <t>Alonso</t>
+  </si>
+  <si>
+    <t>mqptec@gmail.com</t>
+  </si>
+  <si>
+    <t>Joaquin</t>
+  </si>
+  <si>
+    <t>ruben_03_15@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ruben</t>
+  </si>
+  <si>
+    <t>robles@jrcrak.pe</t>
+  </si>
+  <si>
+    <t>Yhony</t>
+  </si>
+  <si>
+    <t>gruporuiz2024@gmail.com</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>valentin2000@hotmail.com</t>
+  </si>
+  <si>
+    <t>Valentin</t>
+  </si>
+  <si>
+    <t>susa.floresojeda@gmail.es</t>
+  </si>
+  <si>
+    <t>Hipólita</t>
+  </si>
+  <si>
+    <t>detarqui_proyectos@gmail.com</t>
+  </si>
+  <si>
+    <t>Susana</t>
+  </si>
+  <si>
+    <t>proyectos@gmgsac.com</t>
+  </si>
+  <si>
+    <t>Gabriela</t>
+  </si>
+  <si>
+    <t>administracion@gmgsac.com</t>
+  </si>
+  <si>
+    <t>recursoshumanos@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>Leslie</t>
+  </si>
+  <si>
+    <t>mespinoza@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>Maria</t>
+  </si>
+  <si>
+    <t>mvalderrama@imsa.com.pe</t>
+  </si>
+  <si>
+    <t>Maribel</t>
+  </si>
+  <si>
+    <t>contempo@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>administracion@melyac.com</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>julio.mena@melyac.com</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>vcarranza@vicarsoluciones.com.pe</t>
+  </si>
+  <si>
+    <t>Sintia</t>
+  </si>
+  <si>
+    <t>elias@anahue.com</t>
+  </si>
+  <si>
+    <t>Elias</t>
+  </si>
+  <si>
+    <t>lizerika.0101@gmail.com</t>
+  </si>
+  <si>
+    <t>Liz</t>
+  </si>
+  <si>
+    <t>diegomoncada10@hotmail.com</t>
+  </si>
+  <si>
+    <t>Diego</t>
+  </si>
+  <si>
+    <t>administracion@camporsal.com.pe</t>
+  </si>
+  <si>
+    <t>Elmer</t>
+  </si>
+  <si>
+    <t>d.abanto@davipingenieros.com</t>
+  </si>
+  <si>
+    <t>v.abanto@davipingenieros.com</t>
+  </si>
+  <si>
+    <t>eliohcc30@gmail.com</t>
+  </si>
+  <si>
+    <t>Eleodoro</t>
+  </si>
+  <si>
+    <t>osorioveramarlene23@gmail.com</t>
+  </si>
+  <si>
+    <t>Marlene</t>
+  </si>
+  <si>
+    <t>faridenoemi@gmail.com</t>
+  </si>
+  <si>
+    <t>Faride</t>
+  </si>
+  <si>
+    <t>eurasiapvc.peru@gmail.com</t>
+  </si>
+  <si>
+    <t>Omer</t>
+  </si>
+  <si>
+    <t>czamalloa@fammsa.pe</t>
+  </si>
+  <si>
+    <t>Aura</t>
+  </si>
+  <si>
+    <t>cesar_2408@hotmail.com</t>
+  </si>
+  <si>
+    <t>Cesar</t>
+  </si>
+  <si>
+    <t>glazing.arq@gmail.com</t>
+  </si>
+  <si>
+    <t>irmapadilla.glazingarq@gmail.com</t>
+  </si>
+  <si>
+    <t>Irma</t>
+  </si>
+  <si>
+    <t>administracion@grupodaesmar.com</t>
+  </si>
+  <si>
+    <t>Omar</t>
+  </si>
+  <si>
+    <t>gerencia@grupodaesmar.com</t>
+  </si>
+  <si>
+    <t>Saturnino</t>
+  </si>
+  <si>
+    <t>ndominguez@yoriamsg.com</t>
+  </si>
+  <si>
+    <t>Leyter</t>
+  </si>
+  <si>
+    <t>huachuapintadojohnnyh@gmail.com</t>
+  </si>
+  <si>
+    <t>Johnny</t>
+  </si>
+  <si>
+    <t>loirettemg@gmail.com</t>
+  </si>
+  <si>
+    <t>Loirette</t>
+  </si>
+  <si>
+    <t>amayanec77@gmail.com</t>
+  </si>
+  <si>
+    <t>Amanda</t>
+  </si>
+  <si>
+    <t>emory@ormaquinarias.com.pe</t>
+  </si>
+  <si>
+    <t>Emali</t>
+  </si>
+  <si>
+    <t>orlando@ormaquinarias.com.pe</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>joteprin29@gmail.com</t>
+  </si>
+  <si>
+    <t>velzar@telefonica.net.pe</t>
+  </si>
+  <si>
+    <t>Carthac</t>
+  </si>
+  <si>
+    <t>dveliz@velzar.com.pe</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>hveliz@velzar.com.pe</t>
+  </si>
+  <si>
+    <t>Hernan</t>
+  </si>
+  <si>
+    <t>larce@3g-office.com</t>
+  </si>
+  <si>
+    <t>Luis</t>
+  </si>
+  <si>
+    <t>jose.garcia@andritz.com</t>
+  </si>
+  <si>
+    <t>marcela.marcos@andritz.com</t>
+  </si>
+  <si>
+    <t>Marcela</t>
+  </si>
+  <si>
+    <t>gcristian@gempresarialgelsa.com</t>
+  </si>
+  <si>
+    <t>Cristian</t>
+  </si>
+  <si>
+    <t>hanitalv@gmail.com</t>
+  </si>
+  <si>
+    <t>Johana</t>
+  </si>
+  <si>
+    <t>arnaldo.marrubbio@carpitech.com</t>
+  </si>
+  <si>
+    <t>Arnaldo</t>
+  </si>
+  <si>
+    <t>gianfranco.olortegui@carpitech.com</t>
+  </si>
+  <si>
+    <t>Gianfranco</t>
+  </si>
+  <si>
+    <t>renzo.malca@carpitech.com</t>
+  </si>
+  <si>
+    <t>Renzo</t>
+  </si>
+  <si>
+    <t>casacorperu@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>fanny@casacorperu.com</t>
+  </si>
+  <si>
+    <t>Fanny</t>
+  </si>
+  <si>
+    <t>ruth_zavala70@hotmail.com</t>
+  </si>
+  <si>
+    <t>Ruth</t>
+  </si>
+  <si>
+    <t>casacoroeru@terra.com.pe</t>
+  </si>
+  <si>
+    <t>Veronica</t>
+  </si>
+  <si>
+    <t>dvelasquez@flujolibre.com</t>
+  </si>
+  <si>
+    <t>vahrens@flujolibre.com</t>
+  </si>
+  <si>
+    <t>Valerie</t>
+  </si>
+  <si>
+    <t>fgarcia@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Freddy</t>
+  </si>
+  <si>
+    <t>analista.marketing@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Karol</t>
+  </si>
+  <si>
+    <t>sortiz@gogroup.com.pe</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>ecasahuaman@jmengineering.com.pe</t>
+  </si>
+  <si>
+    <t>jyarlaque@jmengineering.com.pe</t>
+  </si>
+  <si>
+    <t>remcojm@gmail.com</t>
+  </si>
+  <si>
+    <t>Gladys</t>
+  </si>
+  <si>
+    <t>kassiavjrsac@hotmail.com</t>
+  </si>
+  <si>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>roy_1251@hotmail.com</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>remysta95@gmail.com</t>
+  </si>
+  <si>
+    <t>Micheline</t>
+  </si>
+  <si>
+    <t>pedro_venegas_@outlook.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>rusal_toledo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Alfonso</t>
+  </si>
+  <si>
+    <t>fmilla-leon@gmlarquitectos.com.pe</t>
+  </si>
+  <si>
+    <t>Fiorella</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +529,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -103,9 +563,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -113,14 +571,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -424,518 +885,823 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A61" s="4"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
+      <c r="A81" s="3"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
+      <c r="A82" s="3"/>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
+      <c r="A83" s="3"/>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
+      <c r="A84" s="3"/>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
+      <c r="A85" s="3"/>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
+      <c r="A86" s="3"/>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
+      <c r="A87" s="3"/>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
+      <c r="A88" s="1"/>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
+      <c r="A89" s="3"/>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
+      <c r="A90" s="3"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
+      <c r="A91" s="3"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4"/>
+      <c r="A92" s="3"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
+      <c r="A93" s="3"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
+      <c r="A94" s="3"/>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
+      <c r="A95" s="3"/>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
+      <c r="A96" s="3"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
+      <c r="A97" s="3"/>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
+      <c r="A98" s="3"/>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
+      <c r="A99" s="3"/>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
+      <c r="A100" s="3"/>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A101" s="4"/>
+      <c r="A101" s="3"/>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A102" s="4"/>
+      <c r="A102" s="3"/>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A103" s="4"/>
+      <c r="A103" s="3"/>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A104" s="4"/>
+      <c r="A104" s="3"/>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4"/>
+      <c r="A105" s="3"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A106" s="4"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A107" s="4"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A108" s="2"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A109" s="4"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A110" s="4"/>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A111" s="4"/>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A112" s="4"/>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A113" s="4"/>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A114" s="4"/>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A115" s="4"/>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A116" s="4"/>
+      <c r="A106" s="1"/>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A117" s="4"/>
+      <c r="A117" s="1"/>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A118" s="4"/>
+      <c r="A118" s="3"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A119" s="4"/>
+      <c r="A119" s="3"/>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A120" s="4"/>
+      <c r="A120" s="3"/>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A121" s="4"/>
+      <c r="A121" s="3"/>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A122" s="4"/>
+      <c r="A122" s="3"/>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A123" s="4"/>
+      <c r="A123" s="3"/>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A124" s="4"/>
+      <c r="A124" s="3"/>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A125" s="4"/>
+      <c r="A125" s="3"/>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A126" s="2"/>
+      <c r="A126" s="3"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" s="3"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" s="3"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" s="3"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" s="3"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" s="3"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" s="3"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" s="3"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" s="3"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A136" s="3"/>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A137" s="2"/>
+      <c r="A137" s="3"/>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A138" s="4"/>
+      <c r="A138" s="3"/>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A139" s="4"/>
+      <c r="A139" s="3"/>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A140" s="4"/>
+      <c r="A140" s="3"/>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A141" s="4"/>
+      <c r="A141" s="3"/>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A142" s="4"/>
+      <c r="A142" s="3"/>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A143" s="4"/>
+      <c r="A143" s="3"/>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A144" s="4"/>
+      <c r="A144" s="3"/>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A145" s="4"/>
+      <c r="A145" s="3"/>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A146" s="4"/>
+      <c r="A146" s="3"/>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A147" s="4"/>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A148" s="4"/>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A149" s="4"/>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" s="4"/>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A151" s="4"/>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" s="4"/>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" s="4"/>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A154" s="4"/>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" s="4"/>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" s="4"/>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="4"/>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A158" s="4"/>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A159" s="4"/>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A160" s="4"/>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161" s="4"/>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162" s="4"/>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163" s="4"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164" s="4"/>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165" s="4"/>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166" s="4"/>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167" s="2"/>
+      <c r="A147" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
